--- a/data/ChampionsM.xlsx
+++ b/data/ChampionsM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29721"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71803DDE-E2FC-42DC-BF57-DAA16850DA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
-    <sheet name="Jornada 8" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Jornada 8" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>Matchday</t>
   </si>
@@ -41,142 +40,71 @@
     <t>Jornada 8</t>
   </si>
   <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>15/04/2025</t>
+  </si>
+  <si>
+    <t>3:00 PM</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
+    <t>Paris Saint-Germain</t>
+  </si>
+  <si>
+    <t>3:2</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>3:1</t>
+  </si>
+  <si>
     <t>Wednesday</t>
   </si>
   <si>
-    <t>28/01/2026</t>
-  </si>
-  <si>
-    <t>4:00 PM</t>
-  </si>
-  <si>
-    <t>Union SG</t>
-  </si>
-  <si>
-    <t>Atalanta</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Pafos</t>
-  </si>
-  <si>
-    <t>Slavia Praha</t>
-  </si>
-  <si>
-    <t>Ajax</t>
-  </si>
-  <si>
-    <t>Olympiacos</t>
-  </si>
-  <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
-    <t>Copenhagen</t>
+    <t>16/04/2025</t>
+  </si>
+  <si>
+    <t>Internazionale</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>2:2</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
   </si>
   <si>
     <t>Arsenal</t>
   </si>
   <si>
-    <t>Kairat Almaty</t>
-  </si>
-  <si>
-    <t>Leverkusen</t>
-  </si>
-  <si>
-    <t>Villarreal</t>
-  </si>
-  <si>
-    <t>Atlético</t>
-  </si>
-  <si>
-    <t>Bodø/Glimt</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>Real Madrid</t>
-  </si>
-  <si>
-    <t>Liverpool</t>
-  </si>
-  <si>
-    <t>Qarabağ</t>
-  </si>
-  <si>
-    <t>Napoli</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
-  </si>
-  <si>
-    <t>Man City</t>
-  </si>
-  <si>
-    <t>Galatasaray</t>
-  </si>
-  <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>Newcastle</t>
-  </si>
-  <si>
-    <t>Dortmund</t>
-  </si>
-  <si>
-    <t>Inter</t>
-  </si>
-  <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>Juventus</t>
-  </si>
-  <si>
-    <t>Frankfurt</t>
-  </si>
-  <si>
-    <t>Tottenham</t>
-  </si>
-  <si>
-    <t>Club Brugge</t>
-  </si>
-  <si>
-    <t>Marseille</t>
-  </si>
-  <si>
-    <t>PSV</t>
-  </si>
-  <si>
-    <t>Bayern Munich</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>Sporting</t>
+    <t>1:2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -545,17 +473,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -624,7 +551,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -632,22 +559,22 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -655,348 +582,26 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" t="s">
-        <v>47</v>
-      </c>
-      <c r="G19" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>